--- a/backups/proposal-log-2026-03-13.xlsx
+++ b/backups/proposal-log-2026-03-13.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
   <si>
     <t>Estimate Number</t>
   </si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>HK</t>
+  </si>
+  <si>
+    <t>3000</t>
   </si>
   <si>
     <t>2027-02-01</t>
@@ -748,24 +751,24 @@
         <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
@@ -774,7 +777,7 @@
         <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -792,10 +795,10 @@
         <v>20</v>
       </c>
       <c r="K6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/backups/proposal-log-2026-03-13.xlsx
+++ b/backups/proposal-log-2026-03-13.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
   <si>
     <t>Estimate Number</t>
   </si>
@@ -134,9 +134,6 @@
   </si>
   <si>
     <t>2026-03-24</t>
-  </si>
-  <si>
-    <t>HK</t>
   </si>
   <si>
     <t>3000</t>
@@ -745,30 +742,30 @@
         <v>40</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
       </c>
       <c r="K5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" t="s">
         <v>43</v>
-      </c>
-      <c r="L5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
         <v>45</v>
-      </c>
-      <c r="B6" t="s">
-        <v>46</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
@@ -777,13 +774,13 @@
         <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -795,10 +792,10 @@
         <v>20</v>
       </c>
       <c r="K6" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" t="s">
         <v>48</v>
-      </c>
-      <c r="L6" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/backups/proposal-log-2026-03-13.xlsx
+++ b/backups/proposal-log-2026-03-13.xlsx
@@ -97,61 +97,61 @@
     <t>2026-03-18</t>
   </si>
   <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-11-30</t>
+  </si>
+  <si>
+    <t>26-0026</t>
+  </si>
+  <si>
+    <t>Morgan Stanley Tacoma Interior Improvements</t>
+  </si>
+  <si>
+    <t>Washington (SEA)</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>26-0027</t>
+  </si>
+  <si>
+    <t>Arrowhead Regional Med Ctr. (ARMC) DB PS</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>2027-02-01</t>
+  </si>
+  <si>
+    <t>2028-02-29</t>
+  </si>
+  <si>
+    <t>26-0028</t>
+  </si>
+  <si>
+    <t>Burbank Cargo &amp; GSE Buildout</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
     <t>GM</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>2026-11-30</t>
-  </si>
-  <si>
-    <t>26-0026</t>
-  </si>
-  <si>
-    <t>Morgan Stanley Tacoma Interior Improvements</t>
-  </si>
-  <si>
-    <t>Washington (SEA)</t>
-  </si>
-  <si>
-    <t>2026-03-13</t>
-  </si>
-  <si>
-    <t>2026-03-26</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>26-0027</t>
-  </si>
-  <si>
-    <t>Arrowhead Regional Med Ctr. (ARMC) DB PS</t>
-  </si>
-  <si>
-    <t>2026-03-24</t>
-  </si>
-  <si>
-    <t>3000</t>
-  </si>
-  <si>
-    <t>2027-02-01</t>
-  </si>
-  <si>
-    <t>2028-02-29</t>
-  </si>
-  <si>
-    <t>26-0028</t>
-  </si>
-  <si>
-    <t>Burbank Cargo &amp; GSE Buildout</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
   </si>
   <si>
     <t>2026-05-01</t>
@@ -666,7 +666,7 @@
         <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -678,33 +678,33 @@
         <v>20</v>
       </c>
       <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
         <v>29</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
       </c>
       <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
         <v>34</v>
       </c>
-      <c r="F4" t="s">
-        <v>35</v>
-      </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -716,18 +716,18 @@
         <v>20</v>
       </c>
       <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s">
         <v>36</v>
-      </c>
-      <c r="L4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
         <v>38</v>
-      </c>
-      <c r="B5" t="s">
-        <v>39</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -736,36 +736,36 @@
         <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
       </c>
       <c r="K5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" t="s">
         <v>42</v>
-      </c>
-      <c r="L5" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
         <v>44</v>
-      </c>
-      <c r="B6" t="s">
-        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
@@ -774,13 +774,13 @@
         <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>

--- a/backups/proposal-log-2026-03-13.xlsx
+++ b/backups/proposal-log-2026-03-13.xlsx
@@ -97,6 +97,9 @@
     <t>2026-03-18</t>
   </si>
   <si>
+    <t>HK</t>
+  </si>
+  <si>
     <t>2026-04-01</t>
   </si>
   <si>
@@ -149,9 +152,6 @@
   </si>
   <si>
     <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>GM</t>
   </si>
   <si>
     <t>2026-05-01</t>
@@ -666,7 +666,7 @@
         <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -678,33 +678,33 @@
         <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -716,18 +716,18 @@
         <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -736,36 +736,36 @@
         <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
@@ -774,13 +774,13 @@
         <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
